--- a/results/tables/03_env_driven_taxa_clusters/table8_mccv_classification_report.xlsx
+++ b/results/tables/03_env_driven_taxa_clusters/table8_mccv_classification_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,21 +458,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.661 ± 0.137</t>
+          <t>0.891 ± 0.049</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.708 ± 0.202</t>
+          <t>0.854 ± 0.121</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.669 ± 0.141</t>
+          <t>0.868 ± 0.073</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -483,110 +483,135 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.638 ± 0.205</t>
+          <t>0.786 ± 0.259</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.549 ± 0.215</t>
+          <t>1.000 ± 0.000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.564 ± 0.172</t>
+          <t>0.854 ± 0.179</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Cluster 2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.084 ± 0.220</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.154 ± 0.361</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.104 ± 0.255</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Weighted Avg</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.651 ± 0.151</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.635 ± 0.131</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.622 ± 0.137</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.800 ± 0.068</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.799 ± 0.097</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.790 ± 0.078</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Mean accuracy</t>
-        </is>
-      </c>
+      <c r="A7" s="1" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.635 ± 0.131</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Median accuracy</t>
+          <t>Mean accuracy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.6364</t>
+          <t>0.799 ± 0.097</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr"/>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Median accuracy</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.8000</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Note: Classification metrics shown as mean ± standard deviation across 1,000 CV iterations</t>
-        </is>
-      </c>
+      <c r="A10" s="1" t="inlineStr"/>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Note: Classification metrics shown as mean ± standard deviation across 1,000 CV iterations</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
